--- a/ExcelFiles/Deviation.xlsx
+++ b/ExcelFiles/Deviation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\Excel_Github\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89E0F6A0-BE41-4AD2-B94A-7A1C2CA0F9F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA084D0B-C7A2-4662-A242-3881FFA25141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="367" yWindow="1494" windowWidth="25145" windowHeight="11778" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5529" yWindow="1617" windowWidth="19291" windowHeight="11778" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Deviation" sheetId="1" r:id="rId1"/>
